--- a/out/Расшифровка-отчёта-Июнь-2026.xlsx
+++ b/out/Расшифровка-отчёта-Июнь-2026.xlsx
@@ -7852,7 +7852,7 @@
     <row r="9">
       <c r="A9" s="17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B9" s="17" t="inlineStr">
@@ -8022,12 +8022,12 @@
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>ДОХОД ЗА МЕСЯЦ (шаги 1–5)</t>
+          <t>ДОХОД ЗА МЕСЯЦ</t>
         </is>
       </c>
       <c r="C18" s="9" t="n">
@@ -8041,14 +8041,14 @@
       </c>
       <c r="F18" s="16" t="inlineStr">
         <is>
-          <t>шаги 1–5</t>
+          <t>сумма шагов выше</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -8074,7 +8074,7 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -8100,7 +8100,7 @@
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -8119,7 +8119,7 @@
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
-          <t>шаги 6 + 7 − 8</t>
+          <t>доход + остаток − дивиденды − резерв</t>
         </is>
       </c>
     </row>
